--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -5272,7 +5272,7 @@
         <v>135330204</v>
       </c>
       <c r="B42" t="n">
-        <v>57901</v>
+        <v>57929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -5272,7 +5272,7 @@
         <v>135330204</v>
       </c>
       <c r="B42" t="n">
-        <v>57929</v>
+        <v>57942</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -5272,7 +5272,7 @@
         <v>135330204</v>
       </c>
       <c r="B42" t="n">
-        <v>57942</v>
+        <v>57944</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -5272,7 +5272,7 @@
         <v>135330204</v>
       </c>
       <c r="B42" t="n">
-        <v>57944</v>
+        <v>57954</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -5272,7 +5272,7 @@
         <v>135330204</v>
       </c>
       <c r="B42" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -5272,7 +5272,7 @@
         <v>135330204</v>
       </c>
       <c r="B42" t="n">
-        <v>57955</v>
+        <v>57956</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
